--- a/backend/data/stations.xlsx
+++ b/backend/data/stations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\GitHub\Agender\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4281F2-0951-44F0-8D98-E82686CEC1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CA1334-249D-4A2C-B531-17EDCA94FD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D05FAC4F-C7E5-4CCB-ADFD-2BBC8930D848}"/>
   </bookViews>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={71901CB6-DF05-4331-AE98-C4FA75EA29FD}</author>
+  </authors>
+  <commentList>
+    <comment ref="A38" authorId="0" shapeId="0" xr:uid="{71901CB6-DF05-4331-AE98-C4FA75EA29FD}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Es nueva</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="64">
   <si>
     <t>Código</t>
   </si>
@@ -128,9 +146,6 @@
     <t>MET_Llaviucu</t>
   </si>
   <si>
-    <t>MET_Mamamag</t>
-  </si>
-  <si>
     <t>MET_SayausiPTAP</t>
   </si>
   <si>
@@ -182,9 +197,6 @@
     <t>PLU_Ricaurte</t>
   </si>
   <si>
-    <t>PLU_ElValle</t>
-  </si>
-  <si>
     <t>Jadan</t>
   </si>
   <si>
@@ -227,17 +239,23 @@
     <t>Burgay</t>
   </si>
   <si>
-    <t>MET_Izhcayrrumi</t>
-  </si>
-  <si>
-    <t>MLI_Saucay</t>
+    <t>Transmison</t>
+  </si>
+  <si>
+    <t>MET_Izhcairumi</t>
+  </si>
+  <si>
+    <t>MLI _Saucay</t>
+  </si>
+  <si>
+    <t>MET_Toreadora</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,16 +263,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -262,12 +309,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -283,6 +367,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Jonnathan Augusto Landi Bermeo" id="{51A9E6D9-72B9-4668-BA7F-64EF311B9FD1}" userId="S::alandi@etapa.net.ec::73eabab8-d5a3-4cdf-b5f8-bb1c199bea91" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,17 +690,26 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A38" dT="2025-12-08T17:50:50.82" personId="{51A9E6D9-72B9-4668-BA7F-64EF311B9FD1}" id="{71901CB6-DF05-4331-AE98-C4FA75EA29FD}">
+    <text>Es nueva</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9707F8-AD5A-42C0-B0C5-C79E6A716013}">
-  <dimension ref="A1:F45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9707F8-AD5A-42C0-B0C5-C79E6A716013}">
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -629,46 +728,61 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>697613.2</v>
+        <v>697613</v>
       </c>
       <c r="D2">
-        <v>9674943.5800000001</v>
-      </c>
-      <c r="F2" t="s">
+        <v>9674944</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3143</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>721839.09</v>
+        <v>721839</v>
       </c>
       <c r="D3">
-        <v>9677520.0299999993</v>
-      </c>
-      <c r="F3" t="s">
+        <v>9677520</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2520</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4">
@@ -677,15 +791,21 @@
       <c r="D4">
         <v>9679251</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="6">
+        <v>2608</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -694,86 +814,113 @@
       <c r="D5">
         <v>9671748</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <v>3700</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6">
-        <v>693426.97</v>
+        <v>693427</v>
       </c>
       <c r="D6">
-        <v>9677232.9700000007</v>
-      </c>
-      <c r="F6" t="s">
+        <v>9677233</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3366</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>696874.22</v>
+        <v>696874</v>
       </c>
       <c r="D7">
-        <v>9674605.2100000009</v>
-      </c>
-      <c r="F7" t="s">
+        <v>9674605</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3259</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C8">
-        <v>706139.72</v>
+        <v>706139</v>
       </c>
       <c r="D8">
-        <v>9674523.3699999992</v>
-      </c>
-      <c r="F8" t="s">
+        <v>9674523</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2951</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C9">
-        <v>692349.31</v>
+        <v>692349</v>
       </c>
       <c r="D9">
-        <v>9681404.6099999994</v>
-      </c>
-      <c r="F9" t="s">
+        <v>9681405</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3592</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C10">
@@ -782,211 +929,272 @@
       <c r="D10">
         <v>9674051</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E10" s="6">
+        <v>3003</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C11">
-        <v>714573.58</v>
+        <v>714574</v>
       </c>
       <c r="D11">
-        <v>9678421.9199999999</v>
-      </c>
-      <c r="F11" t="s">
+        <v>9678422</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2773</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12">
-        <v>712586.44</v>
+        <v>712586</v>
       </c>
       <c r="D12">
-        <v>9682798.8300000001</v>
-      </c>
-      <c r="F12" t="s">
+        <v>9682799</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2780</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>712657.86</v>
+        <v>712658</v>
       </c>
       <c r="D13">
-        <v>9682812.6799999997</v>
-      </c>
-      <c r="F13" t="s">
+        <v>9682813</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2775</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>718315.15</v>
+        <v>718315</v>
       </c>
       <c r="D14">
-        <v>9680366.4199999999</v>
-      </c>
-      <c r="F14" t="s">
+        <v>9680366</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2599</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C15">
-        <v>714625.53</v>
+        <v>714626</v>
       </c>
       <c r="D15">
-        <v>9681639.9499999993</v>
-      </c>
-      <c r="F15" t="s">
+        <v>9681640</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2693</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C16">
-        <v>699522.65</v>
+        <v>699523</v>
       </c>
       <c r="D16">
-        <v>9692425.8499999996</v>
-      </c>
-      <c r="F16" t="s">
+        <v>9692426</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3795</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C17">
-        <v>720227.87</v>
+        <v>720228</v>
       </c>
       <c r="D17">
-        <v>9680900.9900000002</v>
-      </c>
-      <c r="E17">
+        <v>9680901</v>
+      </c>
+      <c r="E17" s="5">
         <v>2652</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C18">
-        <v>705558.63</v>
+        <v>705559</v>
       </c>
       <c r="D18">
-        <v>9685486.9499999993</v>
-      </c>
-      <c r="E18">
+        <v>9685487</v>
+      </c>
+      <c r="E18" s="4">
         <v>3154</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>697606</v>
+      </c>
+      <c r="D19">
+        <v>9692216</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19">
-        <v>699501.03</v>
-      </c>
-      <c r="D19">
-        <v>9687442.4900000002</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>714669</v>
+      </c>
+      <c r="D20">
+        <v>9683686</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2847</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20">
-        <v>714668.98</v>
-      </c>
-      <c r="D20">
-        <v>9683685.6699999999</v>
-      </c>
-      <c r="E20">
-        <v>2847</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21">
         <v>721248</v>
       </c>
       <c r="D21">
-        <v>9677407.9900000002</v>
-      </c>
-      <c r="F21" t="s">
+        <v>9677408</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2528</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22">
@@ -995,32 +1203,44 @@
       <c r="D22">
         <v>9673250</v>
       </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="E22" s="6">
+        <v>2593</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>716518</v>
+      </c>
+      <c r="D23">
+        <v>9663955</v>
+      </c>
+      <c r="E23" s="4">
+        <v>2630</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23">
-        <v>716518.12</v>
-      </c>
-      <c r="D23">
-        <v>9663955.3499999996</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C24">
@@ -1029,15 +1249,21 @@
       <c r="D24">
         <v>9659429</v>
       </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="E24" s="8">
+        <v>2652</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C25">
@@ -1046,15 +1272,21 @@
       <c r="D25">
         <v>9653066</v>
       </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="E25" s="7">
+        <v>3174</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C26">
@@ -1063,15 +1295,21 @@
       <c r="D26">
         <v>9675857</v>
       </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="E26" s="5">
+        <v>2728</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27">
@@ -1080,15 +1318,21 @@
       <c r="D27">
         <v>9689695</v>
       </c>
-      <c r="F27" t="s">
+      <c r="E27" s="5">
+        <v>3386</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28">
@@ -1097,15 +1341,21 @@
       <c r="D28">
         <v>9689259</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E28" s="6">
+        <v>2677</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29">
@@ -1114,298 +1364,363 @@
       <c r="D29">
         <v>9681509</v>
       </c>
-      <c r="F29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="E29" s="5">
+        <v>2476</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>718604</v>
+      </c>
+      <c r="D30">
+        <v>9703574</v>
+      </c>
+      <c r="E30" s="4">
+        <v>3485</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30">
-        <v>718604.28</v>
-      </c>
-      <c r="D30">
-        <v>9703574.1500000004</v>
-      </c>
-      <c r="E30">
-        <v>3485</v>
-      </c>
-      <c r="F30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>714221</v>
+      </c>
+      <c r="D31">
+        <v>9698185</v>
+      </c>
+      <c r="E31" s="4">
+        <v>3434</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31">
-        <v>714220.72</v>
-      </c>
-      <c r="D31">
-        <v>9698184.9800000004</v>
-      </c>
-      <c r="E31">
-        <v>3434</v>
-      </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32">
+        <v>723010</v>
+      </c>
+      <c r="D32">
+        <v>9686686</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2708</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <v>720878</v>
+      </c>
+      <c r="D33">
+        <v>9695102</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2979</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32">
-        <v>723010.03</v>
-      </c>
-      <c r="D32">
-        <v>9686685.5899999999</v>
-      </c>
-      <c r="E32">
-        <v>2708</v>
-      </c>
-      <c r="F32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="B34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34">
+        <v>726028</v>
+      </c>
+      <c r="D34">
+        <v>9684203</v>
+      </c>
+      <c r="E34" s="4">
+        <v>2600</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
+        <v>726519</v>
+      </c>
+      <c r="D35">
+        <v>9674226</v>
+      </c>
+      <c r="E35" s="4">
+        <v>2683</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36">
+        <v>743589</v>
+      </c>
+      <c r="D36">
+        <v>9668097</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2311</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>726677</v>
+      </c>
+      <c r="D37">
+        <v>9646390</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2898</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>728378</v>
+      </c>
+      <c r="D38">
+        <v>9682135</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2422</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>728818</v>
+      </c>
+      <c r="D39">
+        <v>9681930</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2425</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33">
-        <v>720877.92</v>
-      </c>
-      <c r="D33">
-        <v>9695101.9199999999</v>
-      </c>
-      <c r="F33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C40">
+        <v>734846</v>
+      </c>
+      <c r="D40">
+        <v>9685516</v>
+      </c>
+      <c r="E40" s="6">
+        <v>2323</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C34">
-        <v>726028.27</v>
-      </c>
-      <c r="D34">
-        <v>9684203.3599999994</v>
-      </c>
-      <c r="F34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C41">
+        <v>732260</v>
+      </c>
+      <c r="D41">
+        <v>9682764</v>
+      </c>
+      <c r="E41" s="4">
+        <v>2521</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35">
-        <v>726538</v>
-      </c>
-      <c r="D35">
-        <v>9674218</v>
-      </c>
-      <c r="F35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36">
-        <v>726519.22</v>
-      </c>
-      <c r="D36">
-        <v>9674226.4600000009</v>
-      </c>
-      <c r="F36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37">
-        <v>743589.12</v>
-      </c>
-      <c r="D37">
-        <v>9668097.0899999999</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38">
-        <v>726677.11</v>
-      </c>
-      <c r="D38">
-        <v>9646390.1400000006</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39">
-        <v>728377.88</v>
-      </c>
-      <c r="D39">
-        <v>9682134.6400000006</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="C42">
+        <v>723665</v>
+      </c>
+      <c r="D42">
+        <v>9679572</v>
+      </c>
+      <c r="E42" s="4">
+        <v>2516</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40">
-        <v>728817.95</v>
-      </c>
-      <c r="D40">
-        <v>9681929.9700000007</v>
-      </c>
-      <c r="F40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41">
-        <v>734846.39</v>
-      </c>
-      <c r="D41">
-        <v>9685515.8599999994</v>
-      </c>
-      <c r="F41" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42">
-        <v>732259.93</v>
-      </c>
-      <c r="D42">
-        <v>9682764.2200000007</v>
-      </c>
-      <c r="F42" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>672552</v>
+      </c>
+      <c r="D43">
+        <v>9679144</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1896</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43">
-        <v>723664.87</v>
-      </c>
-      <c r="D43">
-        <v>9679571.8800000008</v>
-      </c>
-      <c r="E43">
-        <v>2516</v>
-      </c>
-      <c r="F43" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C44">
-        <v>672552.17</v>
+        <v>729424</v>
       </c>
       <c r="D44">
-        <v>9679143.7699999996</v>
-      </c>
-      <c r="E44">
-        <v>1896</v>
-      </c>
-      <c r="F44" t="s">
+        <v>9706615</v>
+      </c>
+      <c r="E44" s="4">
+        <v>3171</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45">
-        <v>729423.99</v>
-      </c>
-      <c r="D45">
-        <v>9706614.9499999993</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
+      <c r="G44">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/data/stations.xlsx
+++ b/backend/data/stations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\GitHub\Agender\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CA1334-249D-4A2C-B531-17EDCA94FD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F421F99C-E8D7-49E7-9E2B-DCCC8516058A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D05FAC4F-C7E5-4CCB-ADFD-2BBC8930D848}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D05FAC4F-C7E5-4CCB-ADFD-2BBC8930D848}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <t>LIM_YanuncayPntMisicata</t>
   </si>
   <si>
-    <t>MET_CancanRefugio</t>
-  </si>
-  <si>
     <t>Meteorológica</t>
   </si>
   <si>
@@ -242,20 +239,23 @@
     <t>Transmison</t>
   </si>
   <si>
-    <t>MET_Izhcairumi</t>
-  </si>
-  <si>
-    <t>MLI _Saucay</t>
-  </si>
-  <si>
     <t>MET_Toreadora</t>
+  </si>
+  <si>
+    <t>MLI_CancanRefugio</t>
+  </si>
+  <si>
+    <t>MET_Izhcayrrumi</t>
+  </si>
+  <si>
+    <t>MLI_Saucay</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,12 +274,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -346,10 +340,10 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -729,7 +723,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -803,10 +797,10 @@
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>688702</v>
@@ -826,10 +820,10 @@
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>693427</v>
@@ -849,10 +843,10 @@
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>696874</v>
@@ -872,10 +866,10 @@
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>706139</v>
@@ -895,10 +889,10 @@
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>692349</v>
@@ -918,10 +912,10 @@
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C10">
         <v>703342</v>
@@ -941,10 +935,10 @@
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C11">
         <v>714574</v>
@@ -964,7 +958,7 @@
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -979,7 +973,7 @@
         <v>2780</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -987,7 +981,7 @@
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -1002,7 +996,7 @@
         <v>2775</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1010,7 +1004,7 @@
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -1025,7 +1019,7 @@
         <v>2599</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1033,10 +1027,10 @@
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C15">
         <v>714626</v>
@@ -1048,7 +1042,7 @@
         <v>2693</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1056,10 +1050,10 @@
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>699523</v>
@@ -1071,7 +1065,7 @@
         <v>3795</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1079,10 +1073,10 @@
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17">
         <v>720228</v>
@@ -1094,7 +1088,7 @@
         <v>2652</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1102,10 +1096,10 @@
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>705559</v>
@@ -1117,7 +1111,7 @@
         <v>3154</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1125,10 +1119,10 @@
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>697606</v>
@@ -1138,7 +1132,7 @@
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1146,10 +1140,10 @@
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20">
         <v>714669</v>
@@ -1161,7 +1155,7 @@
         <v>2847</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1169,7 +1163,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -1184,7 +1178,7 @@
         <v>2528</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1192,7 +1186,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -1207,7 +1201,7 @@
         <v>2593</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1215,10 +1209,10 @@
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <v>716518</v>
@@ -1230,7 +1224,7 @@
         <v>2630</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1238,10 +1232,10 @@
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>713922</v>
@@ -1253,7 +1247,7 @@
         <v>2652</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1261,10 +1255,10 @@
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25">
         <v>712665</v>
@@ -1276,7 +1270,7 @@
         <v>3174</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1284,10 +1278,10 @@
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>716117</v>
@@ -1299,7 +1293,7 @@
         <v>2728</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1307,7 +1301,7 @@
     </row>
     <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1322,7 +1316,7 @@
         <v>3386</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1330,7 +1324,7 @@
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1345,7 +1339,7 @@
         <v>2677</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1353,7 +1347,7 @@
     </row>
     <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1368,7 +1362,7 @@
         <v>2476</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1376,10 +1370,10 @@
     </row>
     <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30">
         <v>718604</v>
@@ -1391,7 +1385,7 @@
         <v>3485</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1399,10 +1393,10 @@
     </row>
     <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31">
         <v>714221</v>
@@ -1414,7 +1408,7 @@
         <v>3434</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1422,10 +1416,10 @@
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32">
         <v>723010</v>
@@ -1437,7 +1431,7 @@
         <v>2708</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1445,10 +1439,10 @@
     </row>
     <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33">
         <v>720878</v>
@@ -1460,7 +1454,7 @@
         <v>2979</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1468,10 +1462,10 @@
     </row>
     <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34">
         <v>726028</v>
@@ -1483,7 +1477,7 @@
         <v>2600</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1491,10 +1485,10 @@
     </row>
     <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35">
         <v>726519</v>
@@ -1506,7 +1500,7 @@
         <v>2683</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1514,10 +1508,10 @@
     </row>
     <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36">
         <v>743589</v>
@@ -1529,7 +1523,7 @@
         <v>2311</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1537,10 +1531,10 @@
     </row>
     <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37">
         <v>726677</v>
@@ -1552,7 +1546,7 @@
         <v>2898</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1560,7 +1554,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1583,10 +1577,10 @@
     </row>
     <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>728818</v>
@@ -1606,10 +1600,10 @@
     </row>
     <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C40">
         <v>734846</v>
@@ -1629,10 +1623,10 @@
     </row>
     <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C41">
         <v>732260</v>
@@ -1652,10 +1646,10 @@
     </row>
     <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C42">
         <v>723665</v>
@@ -1675,10 +1669,10 @@
     </row>
     <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
         <v>672552</v>
@@ -1690,7 +1684,7 @@
         <v>1896</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -1698,10 +1692,10 @@
     </row>
     <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>729424</v>
@@ -1713,7 +1707,7 @@
         <v>3171</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G44">
         <v>1</v>
